--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>imaging</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -782,7 +785,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>1624: fixed value = imaging</t>
+    <t>1624: fixed value = #imaging</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -859,9 +862,6 @@
   </si>
   <si>
     <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -4774,7 +4774,7 @@
         <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>83</v>
@@ -4813,7 +4813,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4834,10 +4834,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4846,15 +4846,15 @@
         <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4880,14 +4880,14 @@
         <v>203</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4936,7 +4936,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4957,10 +4957,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5000,19 +5000,19 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5061,7 +5061,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5082,10 +5082,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5128,16 +5128,16 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5186,7 +5186,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5207,10 +5207,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5224,13 +5224,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -626,242 +626,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>imaging</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>1624: fixed value = #imaging</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -872,6 +636,34 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -1375,7 +1167,29 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1963,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ63"/>
+  <dimension ref="A1:AQ52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1994,7 +1808,7 @@
     <col min="26" max="26" width="77.36328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -3792,7 +3606,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3810,23 +3624,23 @@
         <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>190</v>
@@ -3853,38 +3667,40 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -3893,16 +3709,20 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
       </c>
@@ -3911,7 +3731,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3926,13 +3746,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3950,19 +3770,19 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>83</v>
@@ -3974,10 +3794,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3988,44 +3808,46 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
       </c>
@@ -4049,61 +3871,59 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4111,10 +3931,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4122,13 +3942,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4137,19 +3957,19 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -4198,13 +4018,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4213,19 +4033,19 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4236,10 +4056,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4250,7 +4070,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4259,18 +4079,20 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4319,19 +4141,19 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4340,13 +4162,13 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4357,21 +4179,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4380,21 +4202,23 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4430,46 +4254,46 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>83</v>
+        <v>246</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4480,14 +4304,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4497,7 +4321,7 @@
         <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>83</v>
@@ -4506,19 +4330,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4567,7 +4391,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4576,25 +4400,25 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4605,10 +4429,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4631,16 +4455,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4690,7 +4514,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4711,13 +4535,13 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>83</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4728,10 +4552,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4742,10 +4566,10 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>83</v>
@@ -4754,17 +4578,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>113</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4774,7 +4598,7 @@
         <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>83</v>
@@ -4813,13 +4637,13 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
@@ -4828,33 +4652,33 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4868,7 +4692,7 @@
         <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
@@ -4877,17 +4701,19 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4936,7 +4762,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4945,28 +4771,28 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>284</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -4974,10 +4800,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4991,28 +4817,28 @@
         <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5037,13 +4863,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5061,7 +4887,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5070,7 +4896,7 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>105</v>
@@ -5082,10 +4908,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5099,21 +4925,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -5122,22 +4948,22 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5162,13 +4988,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5186,13 +5012,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -5204,19 +5030,19 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5224,26 +5050,24 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -5252,19 +5076,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>192</v>
+        <v>312</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5274,7 +5098,7 @@
         <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>83</v>
@@ -5289,13 +5113,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5313,7 +5137,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5334,13 +5158,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5351,46 +5175,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5414,11 +5236,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5436,10 +5260,10 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>93</v>
@@ -5451,22 +5275,22 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5474,10 +5298,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5485,34 +5309,34 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5537,13 +5361,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5561,7 +5385,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5576,19 +5400,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5599,10 +5423,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5613,7 +5437,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5622,19 +5446,19 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5684,13 +5508,13 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -5702,19 +5526,19 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5722,14 +5546,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5745,23 +5569,21 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>348</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5809,7 +5631,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5824,22 +5646,22 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5847,45 +5669,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5934,34 +5756,34 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5972,10 +5794,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5995,20 +5817,18 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6057,7 +5877,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6069,7 +5889,7 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6078,13 +5898,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6095,14 +5915,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6118,21 +5938,21 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6180,7 +6000,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6192,22 +6012,22 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6218,45 +6038,45 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>346</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>349</v>
+        <v>142</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>350</v>
+        <v>148</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6305,37 +6125,37 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>352</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>136</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6343,10 +6163,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6360,7 +6180,7 @@
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>83</v>
@@ -6369,20 +6189,16 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>191</v>
+        <v>380</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6406,13 +6222,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6430,7 +6246,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6439,7 +6255,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6451,10 +6267,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>136</v>
+        <v>384</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6468,21 +6284,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6494,20 +6310,16 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>380</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6531,13 +6343,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6555,16 +6367,16 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6573,19 +6385,19 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6593,10 +6405,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6607,7 +6419,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6619,19 +6431,19 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>379</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6656,13 +6468,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6680,13 +6492,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6698,13 +6510,13 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>385</v>
+        <v>308</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6718,10 +6530,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6732,7 +6544,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6747,15 +6559,17 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6779,13 +6593,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>390</v>
+        <v>322</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6803,13 +6617,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6821,19 +6635,19 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>395</v>
+        <v>308</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6841,10 +6655,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6867,19 +6681,17 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>407</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6904,13 +6716,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6928,7 +6740,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6949,10 +6761,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6966,10 +6778,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6992,17 +6804,15 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7051,7 +6861,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7069,19 +6879,19 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7089,10 +6899,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7103,7 +6913,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -7112,19 +6922,19 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7174,13 +6984,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7192,7 +7002,7 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>421</v>
@@ -7204,7 +7014,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7212,10 +7022,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7235,23 +7045,21 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>429</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7299,7 +7107,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7311,7 +7119,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>430</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7320,10 +7128,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7337,10 +7145,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7351,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7360,19 +7168,23 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7420,19 +7232,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7441,10 +7253,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>435</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7458,21 +7270,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7484,17 +7296,15 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>140</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7543,19 +7353,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>212</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7567,7 +7377,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>207</v>
+        <v>370</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7581,14 +7391,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>436</v>
+        <v>138</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7601,26 +7411,24 @@
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>437</v>
+        <v>140</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7668,7 +7476,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7692,7 +7500,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>136</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7706,42 +7514,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>441</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7789,19 +7601,19 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
@@ -7810,10 +7622,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>136</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7827,10 +7639,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7838,7 +7650,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -7850,19 +7662,23 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7886,13 +7702,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>443</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>444</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7910,16 +7726,16 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7928,16 +7744,16 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>445</v>
+        <v>216</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>450</v>
+        <v>217</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -7948,10 +7764,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7971,22 +7787,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>453</v>
+        <v>280</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>455</v>
+        <v>282</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8011,13 +7827,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8035,7 +7851,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8053,19 +7869,19 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>376</v>
+        <v>287</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8073,10 +7889,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8087,7 +7903,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -8102,16 +7918,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>464</v>
+        <v>293</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8136,13 +7952,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>390</v>
+        <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>465</v>
+        <v>294</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>466</v>
+        <v>295</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8160,16 +7976,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8178,13 +7994,13 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>459</v>
+        <v>136</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>376</v>
+        <v>297</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8198,21 +8014,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8224,17 +8040,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>469</v>
+        <v>300</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>471</v>
+        <v>303</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8259,13 +8077,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8283,13 +8101,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8301,19 +8119,19 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>472</v>
+        <v>308</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8321,10 +8139,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8335,7 +8153,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8347,16 +8165,20 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8404,13 +8226,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8425,10 +8247,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>445</v>
+        <v>363</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>364</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8437,1376 +8259,11 @@
         <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ63">
+  <autoFilter ref="A1:AQ52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9816,7 +8273,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,9 +256,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -649,13 +649,13 @@
     <t>open</t>
   </si>
   <si>
+    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
   </si>
   <si>
     <t>Observation.category:imaging</t>
@@ -1815,13 +1815,13 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2057,19 +2057,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>83</v>
@@ -2679,10 +2679,10 @@
         <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>83</v>
@@ -2802,10 +2802,10 @@
         <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>83</v>
@@ -2925,10 +2925,10 @@
         <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>83</v>
@@ -3050,10 +3050,10 @@
         <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>83</v>
@@ -3164,22 +3164,22 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>83</v>
@@ -3287,19 +3287,19 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>83</v>
@@ -3410,19 +3410,19 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -3535,22 +3535,22 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
@@ -3658,7 +3658,7 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>83</v>
@@ -3667,16 +3667,16 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -3794,13 +3794,13 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -3908,25 +3908,25 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4033,22 +4033,22 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>83</v>
@@ -4162,16 +4162,16 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4281,22 +4281,22 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4406,22 +4406,22 @@
         <v>255</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4535,16 +4535,16 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4652,22 +4652,22 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4780,22 +4780,22 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4908,13 +4908,13 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5030,22 +5030,22 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5158,13 +5158,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5278,22 +5278,22 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5406,13 +5406,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5526,22 +5526,22 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5649,22 +5649,22 @@
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO31" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5777,13 +5777,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5901,10 +5901,10 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6024,10 +6024,10 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6149,10 +6149,10 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6267,13 +6267,13 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -6388,13 +6388,13 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6510,16 +6510,16 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -6635,16 +6635,16 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6764,10 +6764,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6882,13 +6882,13 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7005,13 +7005,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7128,13 +7128,13 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7253,13 +7253,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7377,10 +7377,10 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7500,10 +7500,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7625,10 +7625,10 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7744,19 +7744,19 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7869,22 +7869,22 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7997,13 +7997,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8119,22 +8119,22 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8247,13 +8247,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -907,6 +910,10 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>obs-7
 us-core-2us-core-3</t>
   </si>
@@ -927,6 +934,28 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>1797: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>1798: target not supported</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -951,6 +980,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>1796: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1777,12 +1809,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ52"/>
+  <dimension ref="A1:AR54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1816,12 +1848,13 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1954,6 +1987,9 @@
       <c r="AQ1" t="s" s="1">
         <v>79</v>
       </c>
+      <c r="AR1" t="s" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1964,103 +2000,103 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>89</v>
@@ -2072,1108 +2108,1135 @@
         <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR2" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR3" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR4" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR5" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR6" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR7" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR8" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR9" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR10" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>157</v>
@@ -3182,363 +3245,372 @@
         <v>158</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>83</v>
+        <v>159</v>
+      </c>
+      <c r="AR11" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR12" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR13" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>186</v>
@@ -3553,365 +3625,374 @@
         <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
+      </c>
+      <c r="AR14" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AE15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
+      </c>
+      <c r="AR15" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
+      </c>
+      <c r="AR16" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>215</v>
@@ -3927,122 +4008,125 @@
       </c>
       <c r="AQ17" t="s" s="2">
         <v>219</v>
+      </c>
+      <c r="AR17" t="s" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>226</v>
+        <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>228</v>
@@ -4051,246 +4135,252 @@
         <v>229</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>83</v>
+        <v>230</v>
+      </c>
+      <c r="AR18" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF19" t="s" s="2">
+      <c r="AI19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>83</v>
+      <c r="AR19" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>245</v>
@@ -4299,123 +4389,126 @@
         <v>246</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
+      </c>
+      <c r="AR20" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>258</v>
@@ -4424,121 +4517,124 @@
         <v>259</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
+      </c>
+      <c r="AR21" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>266</v>
@@ -4547,121 +4643,124 @@
         <v>267</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
+      </c>
+      <c r="AR22" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>275</v>
@@ -4670,1768 +4769,1823 @@
         <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>83</v>
+        <v>277</v>
+      </c>
+      <c r="AR23" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>288</v>
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
+        <v>290</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>293</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR25" t="s" s="2">
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>286</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
+        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>311</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>317</v>
+        <v>137</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR27" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH28" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF28" t="s" s="2">
+      <c r="AI28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ28" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
+        <v>319</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH29" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR29" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>339</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>348</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ31" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
+      </c>
+      <c r="AR31" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR33" t="s" s="2">
+        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>367</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>140</v>
+        <v>368</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF34" t="s" s="2">
+      <c r="AI34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AP34" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR34" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>376</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR35" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>381</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR36" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>390</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>391</v>
@@ -6439,462 +6593,472 @@
       <c r="M38" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR38" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR39" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>407</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -6906,23 +7070,23 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>417</v>
@@ -6933,1337 +7097,1620 @@
       <c r="M42" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR42" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR43" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>357</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>83</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH45" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>370</v>
+        <v>431</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR45" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>370</v>
+        <v>444</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR46" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>376</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>218</v>
+        <v>380</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>280</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>448</v>
+        <v>143</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>282</v>
+        <v>149</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>288</v>
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>212</v>
+        <v>332</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>294</v>
+        <v>453</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>295</v>
+        <v>454</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>454</v>
+        <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>136</v>
+        <v>455</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>83</v>
+        <v>219</v>
+      </c>
+      <c r="AR50" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>302</v>
+        <v>458</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>307</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
+        <v>290</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>360</v>
+        <v>463</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR52" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G53" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="S52" t="s" s="2">
+      <c r="H53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="T52" t="s" s="2">
+      <c r="AI53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="U52" t="s" s="2">
+      <c r="H54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH54" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="V52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>83</v>
+      <c r="AI54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ52">
+  <autoFilter ref="A1:AR54">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8273,7 +8720,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI53">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file undefined (#undefined) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-observation-imaging</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -629,6 +629,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -637,34 +662,6 @@
     &lt;code value="imaging"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -3681,7 +3678,7 @@
         <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>84</v>
@@ -3699,23 +3696,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3733,25 +3730,25 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3759,13 +3756,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3809,7 +3806,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3827,10 +3824,10 @@
         <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -3878,10 +3875,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3889,14 +3886,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3918,16 +3915,16 @@
         <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -3952,11 +3949,11 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -3974,7 +3971,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -3995,30 +3992,30 @@
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AQ17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4041,19 +4038,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4102,7 +4099,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4123,19 +4120,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4143,10 +4140,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4169,16 +4166,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4228,7 +4225,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4255,13 +4252,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4269,14 +4266,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4295,19 +4292,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4356,7 +4353,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4377,19 +4374,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4397,14 +4394,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4423,19 +4420,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4484,7 +4481,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4493,31 +4490,31 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4525,10 +4522,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4551,16 +4548,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4610,7 +4607,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4637,13 +4634,13 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AP22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4651,10 +4648,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4677,17 +4674,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4736,7 +4733,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4757,19 +4754,19 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4777,10 +4774,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4803,19 +4800,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4852,17 +4849,17 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4871,45 +4868,45 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>84</v>
@@ -4931,19 +4928,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -4992,7 +4989,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5001,45 +4998,45 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AK25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
@@ -5064,16 +5061,16 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5122,7 +5119,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5131,42 +5128,42 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AK26" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5192,16 +5189,16 @@
         <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5226,14 +5223,14 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
       </c>
@@ -5250,7 +5247,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5259,13 +5256,13 @@
         <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
@@ -5280,7 +5277,7 @@
         <v>137</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5291,14 +5288,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5320,16 +5317,16 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5354,14 +5351,14 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5378,7 +5375,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5402,27 +5399,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5445,19 +5442,19 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5506,7 +5503,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5533,10 +5530,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5547,10 +5544,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5576,13 +5573,13 @@
         <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5608,14 +5605,14 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5632,7 +5629,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5656,27 +5653,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5702,16 +5699,16 @@
         <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5736,14 +5733,14 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5760,7 +5757,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5787,10 +5784,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5801,10 +5798,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5827,16 +5824,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5886,7 +5883,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5910,27 +5907,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AP32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5953,16 +5950,16 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6012,7 +6009,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6036,27 +6033,27 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AP33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6079,19 +6076,19 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6140,7 +6137,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6152,25 +6149,25 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AK34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6181,10 +6178,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6207,13 +6204,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6264,7 +6261,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6294,7 +6291,7 @@
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6305,10 +6302,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6337,7 +6334,7 @@
         <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>143</v>
@@ -6390,7 +6387,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6420,7 +6417,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6431,14 +6428,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6460,10 +6457,10 @@
         <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>143</v>
@@ -6518,7 +6515,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6559,10 +6556,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6585,13 +6582,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6642,7 +6639,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6651,7 +6648,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6669,10 +6666,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6683,10 +6680,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6709,13 +6706,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6766,7 +6763,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6775,7 +6772,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -6793,10 +6790,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6807,10 +6804,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6836,16 +6833,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6873,11 +6870,11 @@
         <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -6894,7 +6891,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6918,13 +6915,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AP40" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6935,10 +6932,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6964,16 +6961,16 @@
         <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -6998,14 +6995,14 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7022,7 +7019,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7046,13 +7043,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AP41" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7063,10 +7060,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7089,17 +7086,17 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7148,7 +7145,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7178,7 +7175,7 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7189,10 +7186,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7215,13 +7212,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7272,7 +7269,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7299,10 +7296,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7313,10 +7310,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7339,16 +7336,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7398,7 +7395,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7425,10 +7422,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7439,10 +7436,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7465,16 +7462,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7524,7 +7521,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7551,10 +7548,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7565,10 +7562,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7591,19 +7588,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7652,7 +7649,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7679,10 +7676,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7693,10 +7690,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7719,13 +7716,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7776,7 +7773,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7806,7 +7803,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7817,10 +7814,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7849,7 +7846,7 @@
         <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -7902,7 +7899,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7932,7 +7929,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -7943,14 +7940,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7972,10 +7969,10 @@
         <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>143</v>
@@ -8030,7 +8027,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8071,10 +8068,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8100,16 +8097,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8134,14 +8131,14 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8158,7 +8155,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>94</v>
@@ -8182,16 +8179,16 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8199,10 +8196,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8225,19 +8222,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="O51" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8286,7 +8283,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8310,27 +8307,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8356,16 +8353,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8390,14 +8387,14 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8414,7 +8411,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8423,7 +8420,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8444,7 +8441,7 @@
         <v>137</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8455,14 +8452,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8484,16 +8481,16 @@
         <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8518,14 +8515,14 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8542,7 +8539,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8566,27 +8563,27 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AP53" t="s" s="2">
+      <c r="AQ53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR53" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8612,16 +8609,16 @@
         <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="N54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8670,7 +8667,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8697,10 +8694,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -629,31 +629,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -662,6 +637,34 @@
     &lt;code value="imaging"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -3678,7 +3681,7 @@
         <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>84</v>
@@ -3696,23 +3699,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3730,7 +3733,7 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -3745,10 +3748,10 @@
         <v>84</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3756,13 +3759,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3806,7 +3809,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3824,10 +3827,10 @@
         <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -3875,10 +3878,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3886,14 +3889,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3915,16 +3918,16 @@
         <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -3949,11 +3952,11 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -3971,7 +3974,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -3992,30 +3995,30 @@
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4038,19 +4041,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4099,7 +4102,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4120,19 +4123,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4140,10 +4143,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4166,16 +4169,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4225,7 +4228,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4252,13 +4255,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4266,14 +4269,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4292,19 +4295,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4353,7 +4356,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4374,19 +4377,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4394,14 +4397,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4420,19 +4423,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4481,7 +4484,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4490,10 +4493,10 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4502,19 +4505,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4522,10 +4525,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4548,16 +4551,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4607,7 +4610,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4634,13 +4637,13 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4648,10 +4651,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4674,17 +4677,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4733,7 +4736,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4754,19 +4757,19 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4774,10 +4777,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4800,19 +4803,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4849,17 +4852,17 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4868,10 +4871,10 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -4883,30 +4886,30 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>84</v>
@@ -4928,19 +4931,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -4989,7 +4992,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4998,13 +5001,13 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
@@ -5013,30 +5016,30 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
@@ -5061,16 +5064,16 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5119,7 +5122,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5128,13 +5131,13 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
@@ -5143,27 +5146,27 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5189,16 +5192,16 @@
         <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5223,13 +5226,13 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5247,7 +5250,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5256,13 +5259,13 @@
         <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
@@ -5277,7 +5280,7 @@
         <v>137</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5288,14 +5291,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5317,16 +5320,16 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5351,13 +5354,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5375,7 +5378,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5399,27 +5402,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5442,19 +5445,19 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5503,7 +5506,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5530,10 +5533,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5544,10 +5547,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5573,13 +5576,13 @@
         <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5605,13 +5608,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -5629,7 +5632,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5653,27 +5656,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5699,16 +5702,16 @@
         <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5733,13 +5736,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5757,7 +5760,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5784,10 +5787,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5798,10 +5801,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5824,16 +5827,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5883,7 +5886,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5907,27 +5910,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5950,16 +5953,16 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6009,7 +6012,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6033,27 +6036,27 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6076,19 +6079,19 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6137,7 +6140,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6149,7 +6152,7 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
@@ -6164,10 +6167,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6178,10 +6181,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6204,13 +6207,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6261,7 +6264,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6291,7 +6294,7 @@
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6302,10 +6305,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6334,7 +6337,7 @@
         <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>143</v>
@@ -6387,7 +6390,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6417,7 +6420,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6428,14 +6431,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6457,10 +6460,10 @@
         <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>143</v>
@@ -6515,7 +6518,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6556,10 +6559,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6582,13 +6585,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6639,7 +6642,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6648,7 +6651,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6666,10 +6669,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6680,10 +6683,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6706,13 +6709,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6763,7 +6766,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6772,7 +6775,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -6790,10 +6793,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6804,10 +6807,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6833,16 +6836,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6870,10 +6873,10 @@
         <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -6891,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6915,13 +6918,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6932,10 +6935,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6961,16 +6964,16 @@
         <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -6995,13 +6998,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7019,7 +7022,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7043,13 +7046,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7060,10 +7063,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7086,17 +7089,17 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7145,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7175,7 +7178,7 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7186,10 +7189,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7212,13 +7215,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7269,7 +7272,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7296,10 +7299,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7310,10 +7313,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7336,16 +7339,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7395,7 +7398,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7422,10 +7425,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7436,10 +7439,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7462,16 +7465,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7521,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7548,10 +7551,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7562,10 +7565,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7588,19 +7591,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7649,7 +7652,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7676,10 +7679,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7690,10 +7693,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7716,13 +7719,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7773,7 +7776,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7803,7 +7806,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7814,10 +7817,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7846,7 +7849,7 @@
         <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -7899,7 +7902,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7929,7 +7932,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -7940,14 +7943,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7969,10 +7972,10 @@
         <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>143</v>
@@ -8027,7 +8030,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8068,10 +8071,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8097,16 +8100,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8131,13 +8134,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8155,7 +8158,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>94</v>
@@ -8179,16 +8182,16 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8196,10 +8199,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8222,19 +8225,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8283,7 +8286,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8307,27 +8310,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8353,16 +8356,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8387,13 +8390,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8411,7 +8414,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8420,7 +8423,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8441,7 +8444,7 @@
         <v>137</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8452,14 +8455,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8481,16 +8484,16 @@
         <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8515,13 +8518,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -8539,7 +8542,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8563,27 +8566,27 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8609,16 +8612,16 @@
         <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8667,7 +8670,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8694,10 +8697,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1809,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR54"/>
+  <dimension ref="A1:AQ54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1848,13 +1845,12 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1987,9 +1983,6 @@
       <c r="AQ1" t="s" s="1">
         <v>79</v>
       </c>
-      <c r="AR1" t="s" s="1">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2000,103 +1993,103 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="M2" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="N2" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>89</v>
@@ -2108,1135 +2101,1108 @@
         <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP7" t="s" s="2">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP8" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>157</v>
@@ -3245,372 +3211,363 @@
         <v>158</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AR11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="AM13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="I14" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="P14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>186</v>
@@ -3625,374 +3582,365 @@
         <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AR14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AF15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AR15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="D16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AA16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H17" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="I17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>215</v>
@@ -4008,125 +3956,122 @@
       </c>
       <c r="AQ17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="I18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>228</v>
@@ -4135,252 +4080,246 @@
         <v>229</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="P20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>245</v>
@@ -4389,126 +4328,123 @@
         <v>246</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="O21" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="P21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AK21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AM21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>258</v>
@@ -4517,124 +4453,121 @@
         <v>259</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>266</v>
@@ -4643,124 +4576,121 @@
         <v>267</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>273</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>275</v>
@@ -4769,121 +4699,118 @@
         <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="P24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>287</v>
@@ -4892,128 +4819,125 @@
         <v>288</v>
       </c>
       <c r="AP24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H25" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="O25" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="P25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>287</v>
@@ -5022,128 +4946,125 @@
         <v>288</v>
       </c>
       <c r="AP25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="D26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H26" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="O26" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="P26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>287</v>
@@ -5152,254 +5073,248 @@
         <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="O27" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="P27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI27" t="s" s="2">
+      <c r="AJ27" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="AP27" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="P28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>316</v>
@@ -5408,252 +5323,246 @@
         <v>317</v>
       </c>
       <c r="AP28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="O29" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="P29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH29" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>326</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z30" t="s" s="2">
+      <c r="AA30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>335</v>
@@ -5662,252 +5571,246 @@
         <v>336</v>
       </c>
       <c r="AP30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="P31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>346</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>353</v>
@@ -5916,124 +5819,121 @@
         <v>354</v>
       </c>
       <c r="AP32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>362</v>
@@ -6042,2147 +5942,2096 @@
         <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="O34" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="P34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>373</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="M36" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH36" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH37" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>395</v>
+        <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AO39" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="P40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>408</v>
+        <v>317</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="O41" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="P41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="AA41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH41" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>408</v>
+        <v>317</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>431</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH45" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH45" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G46" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="P46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>444</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AG47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP47" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH48" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G49" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH49" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G50" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>455</v>
+        <v>216</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>217</v>
@@ -8191,379 +8040,370 @@
         <v>218</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="H51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="O51" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>287</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>288</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G53" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="P53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>316</v>
@@ -8572,145 +8412,139 @@
         <v>317</v>
       </c>
       <c r="AP53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="G54" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K54" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="N54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="P54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AH54" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>373</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR54">
+  <autoFilter ref="A1:AQ54">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to us-core-observation-imaging.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -626,6 +626,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -636,32 +661,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -907,10 +907,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>obs-7
 us-core-2us-core-3</t>
   </si>
@@ -929,28 +925,6 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>1797: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>1798: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1806,12 +1780,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ54"/>
+  <dimension ref="A1:AQ52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3635,7 +3609,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3653,23 +3627,23 @@
         <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>190</v>
@@ -3687,22 +3661,22 @@
         <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -3710,13 +3684,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3760,7 +3734,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3778,10 +3752,10 @@
         <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3814,7 +3788,7 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>83</v>
@@ -3826,10 +3800,10 @@
         <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>83</v>
@@ -4779,14 +4753,16 @@
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>277</v>
@@ -4798,43 +4774,41 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>83</v>
       </c>
@@ -4852,22 +4826,22 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4892,13 +4866,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -4916,7 +4890,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4925,76 +4899,74 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5019,13 +4991,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5043,48 +5015,48 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>289</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5095,10 +5067,10 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -5107,19 +5079,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5144,13 +5116,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5168,22 +5140,22 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
@@ -5192,10 +5164,10 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>136</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5206,21 +5178,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5235,17 +5207,15 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5269,13 +5239,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>212</v>
+        <v>323</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5293,13 +5263,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5314,27 +5284,27 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5345,7 +5315,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5357,19 +5327,19 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>320</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5394,13 +5364,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5418,13 +5388,13 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
@@ -5442,10 +5412,10 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5456,10 +5426,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5482,16 +5452,16 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5517,13 +5487,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5541,7 +5511,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5562,27 +5532,27 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5605,20 +5575,18 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>349</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5642,13 +5610,13 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5666,7 +5634,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5687,27 +5655,27 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5718,7 +5686,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5730,18 +5698,20 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5789,19 +5759,19 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>363</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5810,27 +5780,27 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>355</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5853,17 +5823,15 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5912,7 +5880,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5924,7 +5892,7 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5933,31 +5901,31 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>364</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5976,20 +5944,18 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6037,7 +6003,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6049,22 +6015,22 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6075,42 +6041,46 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6158,19 +6128,19 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6185,7 +6155,7 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6203,14 +6173,14 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6222,17 +6192,15 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>381</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>140</v>
+        <v>382</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6281,19 +6249,19 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6305,10 +6273,10 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -6319,46 +6287,42 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>381</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6412,13 +6376,13 @@
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
@@ -6430,10 +6394,10 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>136</v>
+        <v>390</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6444,10 +6408,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6470,16 +6434,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>389</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6503,13 +6471,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6527,7 +6495,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6536,7 +6504,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6548,13 +6516,13 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>394</v>
+        <v>309</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -6565,10 +6533,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6579,7 +6547,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6591,16 +6559,20 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>389</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6624,13 +6596,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6648,16 +6620,16 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6669,13 +6641,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>398</v>
+        <v>309</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6686,10 +6658,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6712,19 +6684,17 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>408</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6749,13 +6719,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6773,7 +6743,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6794,13 +6764,13 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>317</v>
+        <v>412</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6811,10 +6781,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6825,7 +6795,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6837,20 +6807,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>191</v>
+        <v>367</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6874,37 +6840,37 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
@@ -6919,13 +6885,13 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>317</v>
+        <v>416</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6936,10 +6902,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6950,7 +6916,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6959,21 +6925,21 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7021,13 +6987,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7045,10 +7011,10 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7059,10 +7025,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7073,7 +7039,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7082,18 +7048,20 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7142,13 +7110,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7166,10 +7134,10 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7180,10 +7148,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7206,18 +7174,20 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7265,7 +7235,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7289,10 +7259,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7303,10 +7273,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7317,7 +7287,7 @@
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7326,20 +7296,18 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>367</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>368</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7388,19 +7356,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7412,10 +7380,10 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>437</v>
+        <v>371</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7433,7 +7401,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7449,23 +7417,21 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>140</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>373</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7513,7 +7479,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7525,7 +7491,7 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7537,10 +7503,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>444</v>
+        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7551,42 +7517,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>375</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7634,19 +7604,19 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
@@ -7661,7 +7631,7 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7672,21 +7642,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7695,21 +7665,23 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>140</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7733,13 +7705,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>444</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7757,19 +7729,19 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>83</v>
@@ -7778,16 +7750,16 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>379</v>
+        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7802,38 +7774,38 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>139</v>
+        <v>278</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>280</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>148</v>
+        <v>282</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7882,19 +7854,19 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
@@ -7903,27 +7875,27 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7931,7 +7903,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -7943,22 +7915,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7983,13 +7955,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>452</v>
+        <v>294</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>453</v>
+        <v>295</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8007,16 +7979,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8028,16 +8000,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8045,21 +8017,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8068,22 +8040,22 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>301</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>303</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8108,13 +8080,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8132,13 +8104,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8153,27 +8125,27 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>289</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8184,7 +8156,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8196,19 +8168,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>462</v>
+        <v>361</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8233,13 +8205,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8257,16 +8229,16 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8281,270 +8253,20 @@
         <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>136</v>
+        <v>364</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ54">
+  <autoFilter ref="A1:AQ52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8554,7 +8276,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResult.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResult.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
